--- a/docs/detail-design/11_ThemSuaPhong.xlsx
+++ b/docs/detail-design/11_ThemSuaPhong.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="186">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · THÊM / SỬA PHÒNG</t>
   </si>
@@ -136,6 +136,12 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Nhãn giá "{N} giờ đầu" theo số giờ tối thiểu; ô bắt buộc thiếu tô đỏ + hộp lỗi khi lưu; giới hạn độ dài ô chữ (frontend + backend 400 thay vì 500).</t>
+  </si>
+  <si>
     <t>Ảnh 1. Thêm phòng (đã chọn 2 ảnh, chưa lưu)</t>
   </si>
   <si>
@@ -346,7 +352,7 @@
     <t>selectedRoomType()</t>
   </si>
   <si>
-    <t>Chỉ đọc: 2 giờ đầu, Mỗi giờ thêm, Qua đêm, Theo ngày của hạng.</t>
+    <t>Chỉ đọc: "{số giờ tối thiểu} giờ đầu", Mỗi giờ thêm, Qua đêm, Theo ngày của hạng (nhãn giờ đầu lấy minHours từ GET /room-types/overview, cả ở ô Giá riêng).</t>
   </si>
   <si>
     <t>Hình thức mặc định cho đơn của phòng này</t>
@@ -475,7 +481,7 @@
     <t>2. Lưu phòng</t>
   </si>
   <si>
-    <t>Frontend: form thiếu ô bắt buộc (Số phòng, Tên, Hạng, Số khách ≥ 1) → không gửi (không tô đỏ ô). Giá riêng thiếu mức nào → hộp lỗi.</t>
+    <t>Frontend: form thiếu ô bắt buộc (Số phòng, Tên, Hạng, Số khách ≥ 1) → tô đỏ ô, hộp lỗi "Vui lòng nhập đủ các ô bắt buộc (viền đỏ).", không gửi. Giá riêng thiếu mức nào → hộp lỗi. Ô chữ giới hạn số ký tự theo cột DB (maxlength).</t>
   </si>
   <si>
     <t>Thêm: POST /api/rooms; thành công thì nếu có ảnh chờ → POST /api/rooms/{id}/photos (multipart "files"), rồi về /phong.</t>
@@ -553,20 +559,32 @@
     <t>Không có quyền thực hiện</t>
   </si>
   <si>
+    <t>Thiếu ô bắt buộc</t>
+  </si>
+  <si>
+    <t>frontend</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập đủ các ô bắt buộc (viền đỏ).</t>
+  </si>
+  <si>
+    <t>Ô chữ quá dài (gọi thẳng API)</t>
+  </si>
+  <si>
+    <t>Dữ liệu không hợp lệ — errors.{trường}: "Tối đa N ký tự"</t>
+  </si>
+  <si>
     <t>Lỗi khác</t>
   </si>
   <si>
     <t>Không lưu được phòng, thử lại sau.</t>
-  </si>
-  <si>
-    <t>Lưu ý: frontend không giới hạn độ dài các ô chữ; nhập quá độ dài cột DB sẽ lỗi hệ thống (500).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -598,12 +616,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF64748B"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -658,7 +670,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -682,9 +694,6 @@
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1190,7 +1199,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1921,8 +1930,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -1962,6 +2013,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1981,7 +2036,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2017,7 +2072,7 @@
     </row>
     <row r="67" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B67" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
@@ -2053,7 +2108,7 @@
     </row>
     <row r="102" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B102" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -2089,7 +2144,7 @@
     </row>
     <row r="126" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
@@ -2149,7 +2204,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2185,10 +2240,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -2199,22 +2254,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -2222,12 +2277,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -2240,33 +2295,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -2274,12 +2329,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -2292,33 +2347,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -2326,12 +2381,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -2344,33 +2399,33 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2378,12 +2433,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -2396,33 +2451,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2430,12 +2485,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -2448,33 +2503,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -2482,12 +2537,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -2500,33 +2555,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2534,12 +2589,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -2552,33 +2607,33 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -2586,12 +2641,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -2604,33 +2659,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -2638,12 +2693,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -2656,33 +2711,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -2690,12 +2745,12 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2708,33 +2763,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -2742,12 +2797,12 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -2760,33 +2815,33 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -2794,12 +2849,12 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -2807,38 +2862,38 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
     </row>
-    <row r="14" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="14" ht="82" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="6">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -2846,12 +2901,12 @@
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -2864,33 +2919,33 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -2898,12 +2953,12 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -2916,33 +2971,33 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -2950,12 +3005,12 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2968,33 +3023,33 @@
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -3002,12 +3057,12 @@
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -3020,33 +3075,33 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R18" s="3"/>
       <c r="S18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
@@ -3054,12 +3109,12 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -3072,33 +3127,33 @@
         <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -3106,12 +3161,12 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -3121,7 +3176,7 @@
     </row>
     <row r="21" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -3157,10 +3212,10 @@
     </row>
     <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -3171,22 +3226,22 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P22" s="5"/>
       <c r="Q22" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -3194,12 +3249,12 @@
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
       <c r="Y22" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
       <c r="AB22" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC22" s="5"/>
       <c r="AD22" s="5"/>
@@ -3212,33 +3267,33 @@
         <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -3246,12 +3301,12 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
       <c r="AB23" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -3261,7 +3316,7 @@
     </row>
     <row r="25" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -3297,10 +3352,10 @@
     </row>
     <row r="26" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -3311,22 +3366,22 @@
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P26" s="5"/>
       <c r="Q26" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R26" s="5"/>
       <c r="S26" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
@@ -3334,12 +3389,12 @@
       <c r="W26" s="5"/>
       <c r="X26" s="5"/>
       <c r="Y26" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z26" s="5"/>
       <c r="AA26" s="5"/>
       <c r="AB26" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC26" s="5"/>
       <c r="AD26" s="5"/>
@@ -3352,33 +3407,33 @@
         <v>19</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -3386,12 +3441,12 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
       <c r="AB27" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -3401,7 +3456,7 @@
     </row>
     <row r="29" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -3437,10 +3492,10 @@
     </row>
     <row r="30" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
@@ -3451,22 +3506,22 @@
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T30" s="5"/>
       <c r="U30" s="5"/>
@@ -3474,12 +3529,12 @@
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
       <c r="Y30" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z30" s="5"/>
       <c r="AA30" s="5"/>
       <c r="AB30" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC30" s="5"/>
       <c r="AD30" s="5"/>
@@ -3492,33 +3547,33 @@
         <v>20</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P31" s="3"/>
       <c r="Q31" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R31" s="3"/>
       <c r="S31" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
@@ -3526,12 +3581,12 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
       <c r="Y31" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3"/>
       <c r="AB31" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
@@ -3747,7 +3802,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG23"/>
+  <dimension ref="B1:AG24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -3756,7 +3811,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3792,7 +3847,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -3828,10 +3883,10 @@
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3866,10 +3921,10 @@
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -3904,7 +3959,7 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3938,12 +3993,12 @@
       <c r="AF6" s="4"/>
       <c r="AG6" s="4"/>
     </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="7" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -3978,10 +4033,10 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -4016,10 +4071,10 @@
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
@@ -4054,10 +4109,10 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -4092,10 +4147,10 @@
     </row>
     <row r="11" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -4130,10 +4185,10 @@
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
@@ -4168,7 +4223,7 @@
     </row>
     <row r="14" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -4204,7 +4259,7 @@
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -4218,11 +4273,11 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O15" s="5"/>
       <c r="P15" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
@@ -4244,7 +4299,7 @@
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4262,7 +4317,7 @@
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -4284,7 +4339,7 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4298,11 +4353,11 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O17" s="3"/>
       <c r="P17" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -4324,7 +4379,7 @@
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4342,7 +4397,7 @@
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -4364,7 +4419,7 @@
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4382,7 +4437,7 @@
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -4404,7 +4459,7 @@
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -4422,7 +4477,7 @@
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
@@ -4444,7 +4499,7 @@
     </row>
     <row r="21" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -4462,7 +4517,7 @@
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
@@ -4484,7 +4539,7 @@
     </row>
     <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -4498,11 +4553,11 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3" t="s">
-        <v>53</v>
+        <v>180</v>
       </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
@@ -4523,43 +4578,87 @@
       <c r="AG22" s="3"/>
     </row>
     <row r="23" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B23" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9"/>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="9"/>
-      <c r="AD23" s="9"/>
-      <c r="AE23" s="9"/>
-      <c r="AF23" s="9"/>
-      <c r="AG23" s="9"/>
+      <c r="B23" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="6">
+        <v>400</v>
+      </c>
+      <c r="O23" s="6"/>
+      <c r="P23" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+    </row>
+    <row r="24" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="42">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:AG2"/>
     <mergeCell ref="C3:AG3"/>
@@ -4596,7 +4695,12 @@
     <mergeCell ref="B22:M22"/>
     <mergeCell ref="N22:O22"/>
     <mergeCell ref="P22:AG22"/>
-    <mergeCell ref="B23:AG23"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:AG23"/>
+    <mergeCell ref="B24:M24"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P24:AG24"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
